--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_CALVO BASKET XIRIA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_CALVO BASKET XIRIA.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.5279</v>
+        <v>5.5289</v>
       </c>
       <c r="E2" t="n">
-        <v>6.6928</v>
+        <v>6.9612</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.1649</v>
+        <v>-1.4323</v>
       </c>
       <c r="G2" t="n">
-        <v>2.4265</v>
+        <v>2.4508</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.8005</v>
+        <v>-0.7651</v>
       </c>
       <c r="I2" t="n">
-        <v>3.227</v>
+        <v>3.2159</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5068</v>
+        <v>3.673</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.4926</v>
+        <v>-0.3796</v>
       </c>
       <c r="L2" t="n">
-        <v>3.9994</v>
+        <v>4.0526</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.0803</v>
+        <v>-1.2222</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.3079</v>
+        <v>-0.3855</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.7725</v>
+        <v>-0.8368</v>
       </c>
       <c r="P2" t="n">
-        <v>2.2006</v>
+        <v>2.1421</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2006</v>
+        <v>2.1421</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3813</v>
+        <v>0.377</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2669</v>
+        <v>0.287</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1143</v>
+        <v>0.09</v>
       </c>
       <c r="V2" t="n">
-        <v>0.5196</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="W2" t="n">
-        <v>2.9191</v>
+        <v>3.0011</v>
       </c>
       <c r="X2" t="n">
-        <v>-2.3995</v>
+        <v>-2.4421</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9947</v>
+        <v>2.9542</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8199</v>
+        <v>1.0427</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1748</v>
+        <v>1.9115</v>
       </c>
       <c r="G3" t="n">
-        <v>-3.5838</v>
+        <v>-3.4778</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.8727</v>
+        <v>-2.7662</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.7111</v>
+        <v>-0.7116</v>
       </c>
       <c r="J3" t="n">
-        <v>-3.039</v>
+        <v>-2.7938</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.5648</v>
+        <v>-2.3808</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.4742</v>
+        <v>-0.413</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5448</v>
+        <v>-0.6841</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3079</v>
+        <v>-0.3855</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2369</v>
+        <v>-0.2986</v>
       </c>
       <c r="P3" t="n">
-        <v>2.4007</v>
+        <v>2.3368</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.4007</v>
+        <v>2.3368</v>
       </c>
       <c r="S3" t="n">
-        <v>4.1778</v>
+        <v>4.0952</v>
       </c>
       <c r="T3" t="n">
-        <v>3.5992</v>
+        <v>3.557</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5787</v>
+        <v>0.5382</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0118</v>
+        <v>-0.0275</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3421</v>
+        <v>0.3569</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3303</v>
+        <v>-0.3843</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1287</v>
+        <v>-0.1405</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.08</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0488</v>
+        <v>-0.0584</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3999</v>
+        <v>0.4095</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3199</v>
+        <v>0.3284</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5286</v>
+        <v>-0.55</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3999</v>
+        <v>-0.4105</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1287</v>
+        <v>-0.1395</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0002</v>
+        <v>0.003</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0578</v>
+        <v>-0.0526</v>
       </c>
       <c r="U4" t="n">
-        <v>0.058</v>
+        <v>0.0557</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="5">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0742</v>
+        <v>-0.0673</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.7453</v>
+        <v>-0.666</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6711</v>
+        <v>0.5988</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.1002</v>
+        <v>-2.0951</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.831</v>
+        <v>-0.8405</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.2692</v>
+        <v>-1.2545</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.914</v>
+        <v>-1.8714</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.638</v>
+        <v>-0.6235000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.276</v>
+        <v>-1.248</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1862</v>
+        <v>-0.2236</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.193</v>
+        <v>-0.2171</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0069</v>
+        <v>-0.0066</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.8002</v>
+        <v>-0.7789</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="S5" t="n">
-        <v>1.6265</v>
+        <v>1.5857</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9693000000000001</v>
+        <v>0.958</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6572</v>
+        <v>0.6277</v>
       </c>
       <c r="V5" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,40 +877,40 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3334</v>
+        <v>-0.4142</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0911</v>
+        <v>0.0916</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4245</v>
+        <v>-0.5058</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2269</v>
+        <v>0.214</v>
       </c>
       <c r="H6" t="n">
-        <v>0.09130000000000001</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1356</v>
+        <v>0.1329</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02</v>
+        <v>0.0205</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02</v>
+        <v>0.0205</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2069</v>
+        <v>0.1934</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0713</v>
+        <v>0.0605</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1356</v>
+        <v>0.1329</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -922,28 +922,28 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2192</v>
+        <v>0.2102</v>
       </c>
       <c r="T6" t="n">
         <v>0.0711</v>
       </c>
       <c r="U6" t="n">
-        <v>0.148</v>
+        <v>0.1392</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.7794</v>
+        <v>-0.8384</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.7794</v>
+        <v>-0.8384</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. ROQUE DO VALE CARVAHAL</t>
+          <t>C. VARELA ROMERO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5588</v>
+        <v>-0.622</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7543</v>
+        <v>-0.0861</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1954</v>
+        <v>-0.5359</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.2801</v>
+        <v>0.8288</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9797</v>
+        <v>-1.2434</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.3004</v>
+        <v>2.0722</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.9282</v>
+        <v>2.4918</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.6141</v>
+        <v>-0.5567</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.3141</v>
+        <v>3.0485</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6481</v>
+        <v>-1.663</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6344</v>
+        <v>-0.6867</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0137</v>
+        <v>-0.9762</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6002</v>
+        <v>-0.9737</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0003</v>
+        <v>-3.8947</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6005</v>
+        <v>2.921</v>
       </c>
       <c r="S7" t="n">
-        <v>3.2608</v>
+        <v>-0.374</v>
       </c>
       <c r="T7" t="n">
-        <v>2.9145</v>
+        <v>-0.4116</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3464</v>
+        <v>0.0376</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.1398</v>
+        <v>-0.1032</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2598</v>
+        <v>1.7284</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.3995</v>
+        <v>-1.8316</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. VARELA ROMERO</t>
+          <t>P. ROQUE DO VALE CARVAHAL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7829</v>
+        <v>-0.6656</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.599</v>
+        <v>-0.6375</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1839</v>
+        <v>-0.0281</v>
       </c>
       <c r="G8" t="n">
-        <v>0.759</v>
+        <v>-2.283</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.1927</v>
+        <v>-1.0058</v>
       </c>
       <c r="I8" t="n">
-        <v>1.9517</v>
+        <v>-1.2772</v>
       </c>
       <c r="J8" t="n">
-        <v>2.2185</v>
+        <v>-2.8265</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6344</v>
+        <v>-1.5625</v>
       </c>
       <c r="L8" t="n">
-        <v>2.8529</v>
+        <v>-1.264</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.4595</v>
+        <v>0.5436</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5583</v>
+        <v>0.5567</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9012</v>
+        <v>-0.0131</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.0003</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.0011</v>
+        <v>-0.9737</v>
       </c>
       <c r="R8" t="n">
-        <v>3.0009</v>
+        <v>1.5579</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.381</v>
+        <v>3.1958</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4555</v>
+        <v>2.8832</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0745</v>
+        <v>0.3126</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.1606</v>
+        <v>-2.1626</v>
       </c>
       <c r="W8" t="n">
-        <v>1.639</v>
+        <v>0.2795</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.7997</v>
+        <v>-2.4421</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.439</v>
+        <v>-1.4982</v>
       </c>
       <c r="E9" t="n">
-        <v>1.2903</v>
+        <v>1.3809</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.7293</v>
+        <v>-2.8791</v>
       </c>
       <c r="G9" t="n">
-        <v>0.007</v>
+        <v>-0.0192</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9597</v>
+        <v>-0.9853</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9667</v>
+        <v>0.9661</v>
       </c>
       <c r="J9" t="n">
-        <v>1.3216</v>
+        <v>1.3702</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.0382</v>
+        <v>-0.0077</v>
       </c>
       <c r="L9" t="n">
-        <v>1.3598</v>
+        <v>1.3779</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.3146</v>
+        <v>-1.3894</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9215</v>
+        <v>-0.9776</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3931</v>
+        <v>-0.4118</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1864</v>
+        <v>-0.1732</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3691</v>
+        <v>0.3738</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5555</v>
+        <v>-0.547</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.4596</v>
+        <v>-1.5005</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5999</v>
+        <v>0.6105</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.0594</v>
+        <v>-2.1111</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4308</v>
+        <v>-2.4279</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.4353</v>
+        <v>-3.2632</v>
       </c>
       <c r="F10" t="n">
-        <v>1.0045</v>
+        <v>0.8353</v>
       </c>
       <c r="G10" t="n">
-        <v>-5.6695</v>
+        <v>-5.652</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.1068</v>
+        <v>-3.1138</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.5627</v>
+        <v>-2.5382</v>
       </c>
       <c r="J10" t="n">
-        <v>-5.304</v>
+        <v>-5.1929</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.592</v>
+        <v>-2.5349</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.712</v>
+        <v>-2.658</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.3654</v>
+        <v>-0.4591</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5147</v>
+        <v>-0.5789</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1493</v>
+        <v>0.1198</v>
       </c>
       <c r="P10" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2984</v>
+        <v>0.3088</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4092</v>
+        <v>0.4292</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1108</v>
+        <v>-0.1204</v>
       </c>
       <c r="V10" t="n">
-        <v>1.5399</v>
+        <v>1.5521</v>
       </c>
       <c r="W10" t="n">
-        <v>1.4596</v>
+        <v>1.5005</v>
       </c>
       <c r="X10" t="n">
-        <v>0.0803</v>
+        <v>0.0516</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.4809</v>
+        <v>-3.4095</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.8782</v>
+        <v>-5.4477</v>
       </c>
       <c r="F11" t="n">
-        <v>2.3973</v>
+        <v>2.0382</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.4808</v>
+        <v>-1.4306</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1094</v>
+        <v>0.0682</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.5903</v>
+        <v>-1.4988</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2212</v>
+        <v>0.0271</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6034</v>
+        <v>0.6826</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.8247</v>
+        <v>-0.6555</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.2596</v>
+        <v>-1.4577</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.494</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.7655999999999999</v>
+        <v>-0.8433</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.2003</v>
+        <v>-1.1684</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.0011</v>
+        <v>-3.8947</v>
       </c>
       <c r="R11" t="n">
-        <v>2.8008</v>
+        <v>2.7263</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2202</v>
+        <v>-1.1931</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.6558</v>
+        <v>-1.58</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4357</v>
+        <v>0.387</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4204</v>
+        <v>0.3826</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4204</v>
+        <v>0.3826</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.4029</v>
+        <v>-6.3961</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.8281</v>
+        <v>-4.7106</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.5748</v>
+        <v>-1.6855</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.7693</v>
+        <v>-3.758</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.8338</v>
+        <v>-2.8146</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9355</v>
+        <v>-0.9434</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.39</v>
+        <v>-3.3225</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.712</v>
+        <v>-2.658</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.678</v>
+        <v>-0.6645</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.3793</v>
+        <v>-0.4355</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1218</v>
+        <v>-0.1565</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.2575</v>
+        <v>-0.2789</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R12" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.974</v>
+        <v>-0.9429</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4378</v>
+        <v>-0.4144</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5362</v>
+        <v>-0.5285</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.4596</v>
+        <v>-1.5005</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.4596</v>
+        <v>-1.5005</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.968500000000001</v>
+        <v>-7.045199999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.004</v>
+        <v>-4.9778</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0354000000000001</v>
+        <v>-2.0672</v>
       </c>
       <c r="G13" t="n">
-        <v>-15.593</v>
+        <v>-15.3626</v>
       </c>
       <c r="H13" t="n">
-        <v>-13.4562</v>
+        <v>-13.4675</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.137</v>
+        <v>-1.895</v>
       </c>
       <c r="J13" t="n">
-        <v>-9.329599999999999</v>
+        <v>-8.015000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>-10.3428</v>
+        <v>-9.6722</v>
       </c>
       <c r="L13" t="n">
-        <v>1.0131</v>
+        <v>1.6571</v>
       </c>
       <c r="M13" t="n">
-        <v>-6.2633</v>
+        <v>-7.347600000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>-3.1133</v>
+        <v>-3.7955</v>
       </c>
       <c r="O13" t="n">
-        <v>-3.15</v>
+        <v>-3.5521</v>
       </c>
       <c r="P13" t="n">
-        <v>4.0012</v>
+        <v>3.8948</v>
       </c>
       <c r="Q13" t="n">
-        <v>-12.0034</v>
+        <v>-11.6842</v>
       </c>
       <c r="R13" t="n">
-        <v>16.0046</v>
+        <v>15.5788</v>
       </c>
       <c r="S13" t="n">
-        <v>7.202599999999999</v>
+        <v>7.092500000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>5.9924</v>
+        <v>6.100700000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>1.2103</v>
+        <v>0.9920999999999998</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.5791</v>
+        <v>-2.6699</v>
       </c>
       <c r="W13" t="n">
-        <v>8.337</v>
+        <v>8.620600000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-10.916</v>
+        <v>-11.2906</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_CALVO BASKET XIRIA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_CALVO BASKET XIRIA.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.5289</v>
+        <v>6.0529</v>
       </c>
       <c r="E2" t="n">
-        <v>6.9612</v>
+        <v>7.346</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.4323</v>
+        <v>-1.2931</v>
       </c>
       <c r="G2" t="n">
         <v>2.4508</v>
@@ -610,13 +610,13 @@
         <v>2.1421</v>
       </c>
       <c r="S2" t="n">
-        <v>0.377</v>
+        <v>0.901</v>
       </c>
       <c r="T2" t="n">
-        <v>0.287</v>
+        <v>0.6719000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>0.09</v>
+        <v>0.2291</v>
       </c>
       <c r="V2" t="n">
         <v>0.5590000000000001</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9542</v>
+        <v>1.4012</v>
       </c>
       <c r="E3" t="n">
-        <v>1.0427</v>
+        <v>-0.5659999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9115</v>
+        <v>1.9672</v>
       </c>
       <c r="G3" t="n">
         <v>-3.4778</v>
@@ -688,13 +688,13 @@
         <v>2.3368</v>
       </c>
       <c r="S3" t="n">
-        <v>4.0952</v>
+        <v>2.5422</v>
       </c>
       <c r="T3" t="n">
-        <v>3.557</v>
+        <v>1.9483</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5382</v>
+        <v>0.5939</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. LUACES PENIN</t>
+          <t>C. VARELA ROMERO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0275</v>
+        <v>0.6662</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3569</v>
+        <v>1.2577</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3843</v>
+        <v>-0.5915</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1405</v>
+        <v>0.8288</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.08210000000000001</v>
+        <v>-1.2434</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0584</v>
+        <v>2.0722</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4095</v>
+        <v>2.4918</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3284</v>
+        <v>-0.5567</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08110000000000001</v>
+        <v>3.0485</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.55</v>
+        <v>-1.663</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4105</v>
+        <v>-0.6867</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1395</v>
+        <v>-0.9762</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3895</v>
+        <v>-0.9737</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-3.8947</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3895</v>
+        <v>2.921</v>
       </c>
       <c r="S4" t="n">
-        <v>0.003</v>
+        <v>0.9142</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0526</v>
+        <v>0.9322</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0557</v>
+        <v>-0.018</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2795</v>
+        <v>-0.1032</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.7284</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2795</v>
+        <v>-1.8316</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. GARCIA FRAGA</t>
+          <t>I. LUACES PENIN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0673</v>
+        <v>0.2175</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.666</v>
+        <v>0.5184</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5988</v>
+        <v>-0.3009</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.0951</v>
+        <v>-0.1405</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.8405</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.2545</v>
+        <v>-0.0584</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.8714</v>
+        <v>0.4095</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.6235000000000001</v>
+        <v>0.3284</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.248</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2236</v>
+        <v>-0.55</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2171</v>
+        <v>-0.4105</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0066</v>
+        <v>-0.1395</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.7789</v>
+        <v>0.3895</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9737</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1947</v>
+        <v>0.3895</v>
       </c>
       <c r="S5" t="n">
-        <v>1.5857</v>
+        <v>0.248</v>
       </c>
       <c r="T5" t="n">
-        <v>0.958</v>
+        <v>0.1089</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6277</v>
+        <v>0.1391</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2211</v>
+        <v>-0.2795</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2211</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4142</v>
+        <v>-0.3702</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0916</v>
+        <v>0.1913</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5058</v>
+        <v>-0.5615</v>
       </c>
       <c r="G6" t="n">
         <v>0.214</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2102</v>
+        <v>0.2543</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0711</v>
+        <v>0.1707</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1392</v>
+        <v>0.0835</v>
       </c>
       <c r="V6" t="n">
         <v>-0.8384</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. VARELA ROMERO</t>
+          <t>M. GARCIA FRAGA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.622</v>
+        <v>-1.1151</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0861</v>
+        <v>-1.4634</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5359</v>
+        <v>0.3483</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8288</v>
+        <v>-2.0951</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.2434</v>
+        <v>-0.8405</v>
       </c>
       <c r="I7" t="n">
-        <v>2.0722</v>
+        <v>-1.2545</v>
       </c>
       <c r="J7" t="n">
-        <v>2.4918</v>
+        <v>-1.8714</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.5567</v>
+        <v>-0.6235000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>3.0485</v>
+        <v>-1.248</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.663</v>
+        <v>-0.2236</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6867</v>
+        <v>-0.2171</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9762</v>
+        <v>-0.0066</v>
       </c>
       <c r="P7" t="n">
+        <v>-0.7789</v>
+      </c>
+      <c r="Q7" t="n">
         <v>-0.9737</v>
       </c>
-      <c r="Q7" t="n">
-        <v>-3.8947</v>
-      </c>
       <c r="R7" t="n">
-        <v>2.921</v>
+        <v>0.1947</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.374</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4116</v>
+        <v>0.1606</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0376</v>
+        <v>0.3772</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1032</v>
+        <v>1.2211</v>
       </c>
       <c r="W7" t="n">
-        <v>1.7284</v>
+        <v>1.2211</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.8316</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. ROQUE DO VALE CARVAHAL</t>
+          <t>A. IGLESIAS FERNANDEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6656</v>
+        <v>-1.4391</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6375</v>
+        <v>-3.2825</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0281</v>
+        <v>1.8434</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.283</v>
+        <v>-1.4306</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.0058</v>
+        <v>0.0682</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.2772</v>
+        <v>-1.4988</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.8265</v>
+        <v>0.0271</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.5625</v>
+        <v>0.6826</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.264</v>
+        <v>-0.6555</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5436</v>
+        <v>-1.4577</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5567</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0131</v>
+        <v>-0.8433</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5842000000000001</v>
+        <v>-1.1684</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9737</v>
+        <v>-3.8947</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5579</v>
+        <v>2.7263</v>
       </c>
       <c r="S8" t="n">
-        <v>3.1958</v>
+        <v>0.7773</v>
       </c>
       <c r="T8" t="n">
-        <v>2.8832</v>
+        <v>0.5852000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3126</v>
+        <v>0.1922</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.1626</v>
+        <v>0.3826</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2795</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.4421</v>
+        <v>0.3826</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. YUBERO ROSALES</t>
+          <t>S. MARTINEZ GRANDA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4982</v>
+        <v>-1.5153</v>
       </c>
       <c r="E9" t="n">
-        <v>1.3809</v>
+        <v>-2.5175</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.8791</v>
+        <v>1.0022</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0192</v>
+        <v>-5.652</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9853</v>
+        <v>-3.1138</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9661</v>
+        <v>-2.5382</v>
       </c>
       <c r="J9" t="n">
-        <v>1.3702</v>
+        <v>-5.1929</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.0077</v>
+        <v>-2.5349</v>
       </c>
       <c r="L9" t="n">
-        <v>1.3779</v>
+        <v>-2.658</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.3894</v>
+        <v>-0.4591</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9776</v>
+        <v>-0.5789</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4118</v>
+        <v>0.1198</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1947</v>
+        <v>1.3632</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9737</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1684</v>
+        <v>1.3632</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1732</v>
+        <v>1.2215</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3738</v>
+        <v>1.1749</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.547</v>
+        <v>0.0466</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.5005</v>
+        <v>1.5521</v>
       </c>
       <c r="W9" t="n">
-        <v>0.6105</v>
+        <v>1.5005</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.1111</v>
+        <v>0.0516</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. MARTINEZ GRANDA</t>
+          <t>S. YUBERO ROSALES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4279</v>
+        <v>-1.5523</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.2632</v>
+        <v>1.2434</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8353</v>
+        <v>-2.7956</v>
       </c>
       <c r="G10" t="n">
-        <v>-5.652</v>
+        <v>-0.0192</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.1138</v>
+        <v>-0.9853</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.5382</v>
+        <v>0.9661</v>
       </c>
       <c r="J10" t="n">
-        <v>-5.1929</v>
+        <v>1.3702</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.5349</v>
+        <v>-0.0077</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.658</v>
+        <v>1.3779</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4591</v>
+        <v>-1.3894</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5789</v>
+        <v>-0.9776</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1198</v>
+        <v>-0.4118</v>
       </c>
       <c r="P10" t="n">
-        <v>1.3632</v>
+        <v>0.1947</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3632</v>
+        <v>1.1684</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3088</v>
+        <v>-0.2273</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4292</v>
+        <v>0.2363</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1204</v>
+        <v>-0.4635</v>
       </c>
       <c r="V10" t="n">
-        <v>1.5521</v>
+        <v>-1.5005</v>
       </c>
       <c r="W10" t="n">
-        <v>1.5005</v>
+        <v>0.6105</v>
       </c>
       <c r="X10" t="n">
-        <v>0.0516</v>
+        <v>-2.1111</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. IGLESIAS FERNANDEZ</t>
+          <t>P. ROQUE DO VALE CARVAHAL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.4095</v>
+        <v>-1.7357</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.4477</v>
+        <v>-1.6241</v>
       </c>
       <c r="F11" t="n">
-        <v>2.0382</v>
+        <v>-0.1116</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.4306</v>
+        <v>-2.283</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0682</v>
+        <v>-1.0058</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.4988</v>
+        <v>-1.2772</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0271</v>
+        <v>-2.8265</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6826</v>
+        <v>-1.5625</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6555</v>
+        <v>-1.264</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.4577</v>
+        <v>0.5436</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.6143999999999999</v>
+        <v>0.5567</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.8433</v>
+        <v>-0.0131</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.1684</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.8947</v>
+        <v>-0.9737</v>
       </c>
       <c r="R11" t="n">
-        <v>2.7263</v>
+        <v>1.5579</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1931</v>
+        <v>2.1257</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.58</v>
+        <v>1.8966</v>
       </c>
       <c r="U11" t="n">
-        <v>0.387</v>
+        <v>0.2291</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3826</v>
+        <v>-2.1626</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.2795</v>
       </c>
       <c r="X11" t="n">
-        <v>0.3826</v>
+        <v>-2.4421</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.3961</v>
+        <v>-5.8003</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.7106</v>
+        <v>-4.2261</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.6855</v>
+        <v>-1.5742</v>
       </c>
       <c r="G12" t="n">
         <v>-3.758</v>
@@ -1390,13 +1390,13 @@
         <v>0.7789</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9429</v>
+        <v>-0.347</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4144</v>
+        <v>0.0702</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5285</v>
+        <v>-0.4172</v>
       </c>
       <c r="V12" t="n">
         <v>-1.5005</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.045199999999999</v>
+        <v>-5.190200000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.9778</v>
+        <v>-3.1228</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.0672</v>
+        <v>-2.067299999999999</v>
       </c>
       <c r="G13" t="n">
         <v>-15.3626</v>
@@ -1438,7 +1438,7 @@
         <v>-13.4675</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.895</v>
+        <v>-1.894999999999999</v>
       </c>
       <c r="J13" t="n">
         <v>-8.015000000000001</v>
@@ -1447,13 +1447,13 @@
         <v>-9.6722</v>
       </c>
       <c r="L13" t="n">
-        <v>1.6571</v>
+        <v>1.657100000000001</v>
       </c>
       <c r="M13" t="n">
         <v>-7.347600000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>-3.7955</v>
+        <v>-3.795499999999999</v>
       </c>
       <c r="O13" t="n">
         <v>-3.5521</v>
@@ -1468,13 +1468,13 @@
         <v>15.5788</v>
       </c>
       <c r="S13" t="n">
-        <v>7.092500000000001</v>
+        <v>8.947700000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>6.100700000000001</v>
+        <v>7.955800000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>0.9920999999999998</v>
+        <v>0.992</v>
       </c>
       <c r="V13" t="n">
         <v>-2.6699</v>
